--- a/artfynd/A 39118-2025 artfynd.xlsx
+++ b/artfynd/A 39118-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89602753</v>
+        <v>89600267</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,19 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öster-Hasslingen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466879.0748680144</v>
+        <v>466874</v>
       </c>
       <c r="R2" t="n">
-        <v>7100131.096356805</v>
+        <v>7100058</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,28 +743,17 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,50 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89600266</v>
+        <v>89602753</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öster-Hasslingen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466879.0748680144</v>
+        <v>466879</v>
       </c>
       <c r="R3" t="n">
-        <v>7100131.096356805</v>
+        <v>7100131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,29 +852,25 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -916,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89600262</v>
+        <v>89602758</v>
       </c>
       <c r="B4" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,34 +902,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öster-Hasslingen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466976.8456890446</v>
+        <v>467211</v>
       </c>
       <c r="R4" t="n">
-        <v>7100201.960535204</v>
+        <v>7099618</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,29 +962,25 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1032,15 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89600267</v>
+        <v>89602768</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,16 +1030,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öster-Hasslingen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466873.9066097036</v>
+        <v>466985</v>
       </c>
       <c r="R5" t="n">
-        <v>7100057.93182298</v>
+        <v>7099817</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,27 +1072,18 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1153,53 +1111,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89602755</v>
+        <v>89600259</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öster-Hasslingen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467272.1221257652</v>
+        <v>467226</v>
       </c>
       <c r="R6" t="n">
-        <v>7099684.967897259</v>
+        <v>7099555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,28 +1179,17 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1273,37 +1212,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89602758</v>
+        <v>89602755</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1316,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467210.8272919251</v>
+        <v>467272</v>
       </c>
       <c r="R7" t="n">
-        <v>7099618.083369263</v>
+        <v>7099685</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,19 +1283,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,11 +1297,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1398,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89600264</v>
+        <v>89602764</v>
       </c>
       <c r="B8" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1414,34 +1328,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öster-Hasslingen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466961.8569622386</v>
+        <v>467299</v>
       </c>
       <c r="R8" t="n">
-        <v>7099864.952682868</v>
+        <v>7099599</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,34 +1388,20 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Sälghögstubbe</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1519,53 +1422,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89602768</v>
+        <v>89600264</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öster-Hasslingen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466985.0558364765</v>
+        <v>466962</v>
       </c>
       <c r="R9" t="n">
-        <v>7099816.912862512</v>
+        <v>7099865</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,34 +1490,23 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Sälghögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1644,37 +1528,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89600265</v>
+        <v>89600266</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1684,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467337.2157347976</v>
+        <v>466879</v>
       </c>
       <c r="R10" t="n">
-        <v>7099611.931901255</v>
+        <v>7100131</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1717,24 +1596,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,53 +1629,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89602764</v>
+        <v>89600265</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öster-Hasslingen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467298.8824568941</v>
+        <v>467337</v>
       </c>
       <c r="R11" t="n">
-        <v>7099599.178887065</v>
+        <v>7099612</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,19 +1697,14 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,7 +1713,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1885,53 +1735,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89602757</v>
+        <v>89600260</v>
       </c>
       <c r="B12" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öster-Hasslingen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467289.9882067068</v>
+        <v>466877</v>
       </c>
       <c r="R12" t="n">
-        <v>7099672.063804098</v>
+        <v>7099963</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1961,28 +1803,17 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1998,6 +1829,212 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>89600262</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Öster-Hasslingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>466977</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7100202</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>89602757</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öster-Hasslingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>467290</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7099672</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
